--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/OHIO_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/OHIO_2011.xlsx
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C104">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C361">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C398">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C627">
